--- a/AAII_Financials/Quarterly/DHLGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DHLGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="92">
   <si>
     <t>DHLGY</t>
   </si>
@@ -656,102 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -794,26 +798,29 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>26334300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25977900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26146000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25365100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -856,26 +863,29 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>14677900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>14765600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14788400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14293800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -918,26 +928,29 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>11656400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11212300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11357600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11071300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1128,8 +1148,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1190,26 +1213,29 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>1232800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1142300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1108800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>989500</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,8 +1255,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1273,26 +1300,29 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>24231000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23785100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23615000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22964000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1335,26 +1365,29 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>2103300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2192700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2530900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2401100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1421,26 +1455,29 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-115200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-164300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-158900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-171400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1492,17 +1529,20 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>6318000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1545,8 +1585,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1563,8 +1603,11 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1607,26 +1650,29 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>1988100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2028500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2372100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2229700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1669,26 +1715,29 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>465200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>587900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>688800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>488300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,8 +1798,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1793,26 +1845,29 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>1523000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1440600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1683300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1741400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1855,26 +1910,29 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>1460900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1318500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1581000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1610100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1979,8 +2040,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2165,26 +2235,29 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>115200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>164300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>158900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>171400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2227,26 +2300,29 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>1460900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1318500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1581000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1610100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,8 +2383,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2351,93 +2430,99 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>1460900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1318500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1581000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1610100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,56 +2570,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4313900</v>
+      </c>
+      <c r="E41" s="3">
         <v>6170900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3963800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4165200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3699400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3746800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3056900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4979000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4033400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4134200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3587300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5383500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4197800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,56 +2633,59 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>588400</v>
+      </c>
+      <c r="E42" s="3">
         <v>2815600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2000700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1023100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>723400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1037600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>637700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>994900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>712500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>959100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>670900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>450900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>486900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>644300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1992600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2608,56 +2698,59 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14997100</v>
+      </c>
+      <c r="E43" s="3">
         <v>13618100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15221300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13429500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13203800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12531300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13406100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12990200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12552200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12330300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13576900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11504000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11980300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12614100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14076500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,56 +2763,59 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1295600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1196800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1185900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1305900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1233100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1128400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1186500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1192300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1188300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1154400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1172800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1141000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1133200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1063700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1026700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2732,56 +2828,59 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3786100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3588100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>706800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3088100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4218400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3063100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>641900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2962300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3274400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3031600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>556000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3498100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3777300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3977600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3441300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,56 +2893,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24981100</v>
+      </c>
+      <c r="E46" s="3">
         <v>27389600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24593200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23011900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23078100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24561200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20858300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21139900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20784300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22454400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21236900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20728200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20965100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23683200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24734900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,56 +2958,59 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2423200</v>
+      </c>
+      <c r="E47" s="3">
         <v>3165000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2227300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2996600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>909000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1613700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>891400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1525800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>804700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1320500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>759400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1322000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1411600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1339600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1431000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2918,56 +3023,59 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36886800</v>
+      </c>
+      <c r="E48" s="3">
         <v>36012900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36020900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35620100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36018800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33400300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31856300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33511000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33095500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32555800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31608300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31254200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31343900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30851800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>31799200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,56 +3088,59 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17102700</v>
+      </c>
+      <c r="E49" s="3">
         <v>17194700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17050600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17014000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17094500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15907900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15086400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16239100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15694800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15823700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15764300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14961900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15334100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15247700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31280800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,56 +3283,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>838600</v>
+      </c>
+      <c r="E52" s="3">
         <v>784000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2136900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>681700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>685800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>631200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2148300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>638000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>590400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>512500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2736800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>545100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>643000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>612800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2238500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,56 +3413,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83434300</v>
+      </c>
+      <c r="E54" s="3">
         <v>85798500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83383800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80667600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>79128600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77421100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72341900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74578400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>72412900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74099700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73869800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70256100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71134300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>73178000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75844000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,56 +3530,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9444800</v>
+      </c>
+      <c r="E57" s="3">
         <v>8713200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9262700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8868900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8746900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8348500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8939800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8660500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8609200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8504700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9372200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8572200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8714000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9196000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11001800</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,56 +3593,59 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4970900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6317300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6699500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6990500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6761000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6288400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5633100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6242500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6593800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4580900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5282400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3995600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4845000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4146000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4965400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,56 +3658,59 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9849200</v>
+      </c>
+      <c r="E59" s="3">
         <v>9976900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3103200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9063700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8893700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8405800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2447500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8320300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7858100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8506900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2666100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8548900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8814400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9694700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8692400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,56 +3723,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24264800</v>
+      </c>
+      <c r="E60" s="3">
         <v>25007500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25139100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24923100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24401600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23042600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21917400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23223300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23061200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21592400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22462700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21116600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22373400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23036700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24659600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,56 +3788,59 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26986200</v>
+      </c>
+      <c r="E61" s="3">
         <v>27184400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25572400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23844900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23633600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22412500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19430600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19865000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19285300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20605200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19828700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19620000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19231400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18939600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19585700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3710,56 +3853,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3637600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3572000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3304000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3456500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3409300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3230700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2927800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3301400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3158700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3056400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2773300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2401600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2378800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2307700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5328700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,56 +4113,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57371200</v>
+      </c>
+      <c r="E66" s="3">
         <v>58298200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56821700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55044000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54373500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51273200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47277200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49358700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48220300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>48018100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48570800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45312200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46521800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46839400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>50107800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,56 +4463,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22171800</v>
+      </c>
+      <c r="E72" s="3">
         <v>23718400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23215900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22471000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21302400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21568300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20155300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20998200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19398900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21338900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20806900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20189500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19656100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21367900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24408200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,56 +4723,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25459800</v>
+      </c>
+      <c r="E76" s="3">
         <v>26980300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26097200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25269300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24240800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25671200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24633000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24829400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23644100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25585300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24842500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24563900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23995600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25771400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25736200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,75 +4853,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4775,26 +4970,29 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>1460900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1318500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1581000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1610100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1316500</v>
+        <v>1397500</v>
       </c>
       <c r="E83" s="3">
+        <v>1165200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1006300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1286000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1249300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1095000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1024600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1179100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1181200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1030000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>914800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1031600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1065200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>964200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>4088300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2305500</v>
+      </c>
+      <c r="E89" s="3">
         <v>3088900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3075000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3064600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2008200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2354100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3175300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2278600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1726100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2158800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2741200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2682000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2018600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2602100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>10842400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,56 +5495,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-759700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-731000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1111900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-733300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-674100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-701500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1033200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-714900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-621500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-773500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1031300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-895400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-865700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-879000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3912000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1104800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1006600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3019800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-986700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-824400</v>
       </c>
-      <c r="H94" s="3">
-        <v>-655000</v>
-      </c>
       <c r="I94" s="3">
+        <v>-653900</v>
+      </c>
+      <c r="J94" s="3">
         <v>-940100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-532000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-439300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-644100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1330800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-591700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-587300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>130400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-5234000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,50 +5780,51 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
+      <c r="D96" s="3">
+        <v>2418600</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3">
         <v>2493200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>2324000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3">
         <v>2407200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5601,16 +5835,19 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1815200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5237100</v>
+      </c>
+      <c r="E100" s="3">
         <v>161400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-265400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1586300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4715200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1270000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1329300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1863700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3176900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-460700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1576200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1450000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3140800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1330900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>-6753000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-158500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-81100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>54900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-63600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-119400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>16900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-112400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-135800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-245800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>50000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>38700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>38900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
         <v>112800</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1799400</v>
+      </c>
+      <c r="E102" s="3">
         <v>2278300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-205500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>469300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-3688800</v>
-      </c>
       <c r="H102" s="3">
-        <v>2888000</v>
+        <v>-3690000</v>
       </c>
       <c r="I102" s="3">
+        <v>2889100</v>
+      </c>
+      <c r="J102" s="3">
         <v>960800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-180700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1889000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1043300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-285200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>657300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1822100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1265800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-1031800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
